--- a/results.xlsx
+++ b/results.xlsx
@@ -456,12 +456,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ukraiński kontrofensywa przebiegać wolniej niż zakładać rozwijać się zgodnie plan powiedzieć minister obrona ukraina ołeksij reznikow cytować poniedziałek ukraiński agencja unianin polityk zapewnić że martwić się rozwój sytuacja front ponieważ błąd zakładać że każdy ofensywa być błyskawiczny reznikow zaznaczyć że czynnik spowalniający atak ukraińca być brak amunicja szczególnie artyleryjski sam system artyleryjski problem obrona powietrzny mieć długi linia front wróg stać droga ważny pozostawać życie ukraiński żołnierz powiedzieć minister obrona ukraina Reznikow zwrócić też uwaga problem zaminować rosyjski pozycja obronny musieć ostrożnie używać saper przyznać poniedziałek siła zbrojny ukraina poinformować że południe kraj obwodz chersoński zneutralizować sześć rosyjski system obrona powietrzny ukraiński armia ocenić że niszczyć system jeden decyduć czynnik walka rosyjski lotnictwo potencjało powietrzny agresor kijowy jakub bawołek pap</t>
+          <t>Ukraińska kontrofensywa przebiega wolniej, niż zakładano, ale rozwija się zgodnie z planem - powiedział minister obrony Ukrainy Ołeksij Reznikow, cytowany w poniedziałek przez ukraińską agencję UNIAN. Polityk zapewnił, że "nie martwi się rozwojem sytuacji na froncie" ponieważ błędem jest zakładanie, że "każda ofensywa musi być błyskawiczna".
+Reznikow zaznaczył, że czynnikami spowalniającymi ataki Ukraińców są: brak amunicji, szczególnie artyleryjskiej, samych systemów artyleryjskich oraz problem obrony powietrznej.
+"Mamy bardzo długie linie frontu i wielu wrogów stojących nam na drodze. Dla nas najważniejsze pozostaje życie ukraińskich żołnierzy" - powiedział minister obrony Ukrainy.
+Reznikow zwrócił też uwagę na problem zaminowania rosyjskich pozycji obronnych. "Musimy bardzo ostrożnie używać naszych saperów" - przyznał.
+W poniedziałek siły zbrojne Ukrainy poinformowały, że na południu kraju - w obwodzie chersońskim - zneutralizowano sześć rosyjskich systemów obrony powietrznej.
+Ukraińska armia oceniła, że niszczenie tych systemów jest jednym z decydujących czynników w walce z rosyjskim lotnictwem i potencjałem powietrznym agresora.
+Z Kijowa Jakub Bawołek (PAP)
+jbw/ kb/</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>trwać dzień rosyjski inwazja ukrainę kontrofensyw przebiegać wolniej niż zakładać rozwijać się zgodnie plan powiedzieć minister obrona ukraina ołeksij reznikow ocena czynnik spowalniający atak ukraińca być brak amunicja szczególnie artyleryjski sam system artyleryjski problem obrona powietrzny zapraszać śledzić relacja żywo</t>
+          <t>Trwa 517. dzień rosyjskiej inwazji na Ukrainę. — Nasza kontrofensywa przebiega wolniej, niż zakładano, ale rozwija się zgodnie z planem — powiedział minister obrony Ukrainy Ołeksij Reznikow. W jego ocenie czynnikami spowalniającymi ataki Ukraińców są: brak amunicji, szczególnie artyleryjskiej, samych systemów artyleryjskich oraz problem obrony powietrznej. Zapraszamy do śledzenia relacji na żywo.</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -470,8 +477,16 @@
       <c r="D2" t="n">
         <v>0.8106715083122253</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Ukraińska, Ukrainy, Ołeksij Reznikow, ukraińską, UNIAN, Reznikow, Ukraińców, ukraińskich, Ukrainy, Reznikow, rosyjskich, Ukrainy, chersońskim, rosyjskich, Ukraińska, rosyjskim, Kijowa, Jakub Bawołek, PAP</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>rosyjskiej, Ukrainę, Ukrainy, Ołeksij Reznikow, Ukraińców</t>
+        </is>
+      </c>
       <c r="G2" t="n">
         <v>0.1875</v>
       </c>
@@ -479,12 +494,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ukraiński kontrofensywa przebiegać wolniej niż zakładać rozwijać się zgodnie plan powiedzieć minister obrona ukraina ołeksij reznikow cytować poniedziałek ukraiński agencja unianin polityk zapewnić że martwić się rozwój sytuacja front ponieważ błąd zakładać że każdy ofensywa być błyskawiczny reznikow zaznaczyć że czynnik spowalniający atak ukraińca być brak amunicja szczególnie artyleryjski sam system artyleryjski problem obrona powietrzny mieć długi linia front wróg stać droga ważny pozostawać życie ukraiński żołnierz powiedzieć minister obrona ukraina Reznikow zwrócić też uwaga problem zaminować rosyjski pozycja obronny musieć ostrożnie używać saper przyznać poniedziałek siła zbrojny ukraina poinformować że południe kraj obwodz chersoński zneutralizować sześć rosyjski system obrona powietrzny ukraiński armia ocenić że niszczyć system jeden decyduć czynnik walka rosyjski lotnictwo potencjało powietrzny agresor kijowy jakub bawołek pap</t>
+          <t>Ukraińska kontrofensywa przebiega wolniej, niż zakładano, ale rozwija się zgodnie z planem - powiedział minister obrony Ukrainy Ołeksij Reznikow, cytowany w poniedziałek przez ukraińską agencję UNIAN. Polityk zapewnił, że "nie martwi się rozwojem sytuacji na froncie" ponieważ błędem jest zakładanie, że "każda ofensywa musi być błyskawiczna".
+Reznikow zaznaczył, że czynnikami spowalniającymi ataki Ukraińców są: brak amunicji, szczególnie artyleryjskiej, samych systemów artyleryjskich oraz problem obrony powietrznej.
+"Mamy bardzo długie linie frontu i wielu wrogów stojących nam na drodze. Dla nas najważniejsze pozostaje życie ukraińskich żołnierzy" - powiedział minister obrony Ukrainy.
+Reznikow zwrócił też uwagę na problem zaminowania rosyjskich pozycji obronnych. "Musimy bardzo ostrożnie używać naszych saperów" - przyznał.
+W poniedziałek siły zbrojne Ukrainy poinformowały, że na południu kraju - w obwodzie chersońskim - zneutralizowano sześć rosyjskich systemów obrony powietrznej.
+Ukraińska armia oceniła, że niszczenie tych systemów jest jednym z decydujących czynników w walce z rosyjskim lotnictwem i potencjałem powietrznym agresora.
+Z Kijowa Jakub Bawołek (PAP)
+jbw/ kb/</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>polityka zapewnić że martwić się rozwój sytuacja front ponieważ błąd zakładać że każdy ofensywa być błyskawiczny reznikow zaznaczyć że czynnik spowalniający atak ukraińca być brak amunicja szczególnie artyleryjski sam system artyleryjski problem obrona powietrzny cenny ludzki życie mieć długi linia front wróg stać droga ważny pozostawać życie ukraiński żołnierz powiedzieć minister obrona ukraina Reznikow zwrócić też uwaga problem zaminować rosyjski pozycja obronny musieć ostrożnie używać saper przyznać poniedziałek siła zbrojny ukraina poinformować że południe kraj obwodz chersoński zneutralizować sześć rosyjski system obrona powietrzny ukraiński armia ocenić że niszczyć system jeden decyduć czynnik walka rosyjski lotnictwo potencjało powietrzny agresor czytać więcej</t>
+          <t>Polityk zapewnił, że "nie martwi się rozwojem sytuacji na froncie" ponieważ błędem jest zakładanie, że "każda ofensywa musi być błyskawiczna".
+Reznikow zaznaczył, że czynnikami spowalniającymi ataki Ukraińców są: brak amunicji, szczególnie artyleryjskiej, samych systemów artyleryjskich oraz problem obrony powietrznej.
+Cenne ludzkie życie
+- Mamy bardzo długie linie frontu i wielu wrogów stojących nam na drodze. Dla nas najważniejsze pozostaje życie ukraińskich żołnierzy - powiedział minister obrony Ukrainy.
+Reznikow zwrócił też uwagę na problem zaminowania rosyjskich pozycji obronnych. - Musimy bardzo ostrożnie używać naszych saperów - przyznał.
+W poniedziałek siły zbrojne Ukrainy poinformowały, że na południu kraju - w obwodzie chersońskim - zneutralizowano sześć rosyjskich systemów obrony powietrznej.
+Ukraińska armia oceniła, że niszczenie tych systemów jest jednym z decydujących czynników w walce z rosyjskim lotnictwem i potencjałem powietrznym agresora.
+Czytaj więcej:
+pap/as</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -493,8 +523,16 @@
       <c r="D3" t="n">
         <v>0.8540468215942383</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Ukraińska, Ukrainy, Ołeksij Reznikow, ukraińską, UNIAN, Reznikow, Ukraińców, ukraińskich, Ukrainy, Reznikow, rosyjskich, Ukrainy, chersońskim, rosyjskich, Ukraińska, rosyjskim, Kijowa, Jakub Bawołek, PAP</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Reznikow, Ukraińców, ukraińskich, Ukrainy, Reznikow, rosyjskich, Ukrainy, chersońskim, rosyjskich, Ukraińska, rosyjskim</t>
+        </is>
+      </c>
       <c r="G3" t="n">
         <v>0.5714285714285714</v>
       </c>
@@ -502,12 +540,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ukraiński kontrofensywa przebiegać wolniej niż zakładać rozwijać się zgodnie plan powiedzieć minister obrona ukraina ołeksij reznikow cytować poniedziałek ukraiński agencja unianin polityk zapewnić że martwić się rozwój sytuacja front ponieważ błąd zakładać że każdy ofensywa być błyskawiczny reznikow zaznaczyć że czynnik spowalniający atak ukraińca być brak amunicja szczególnie artyleryjski sam system artyleryjski problem obrona powietrzny mieć długi linia front wróg stać droga ważny pozostawać życie ukraiński żołnierz powiedzieć minister obrona ukraina Reznikow zwrócić też uwaga problem zaminować rosyjski pozycja obronny musieć ostrożnie używać saper przyznać poniedziałek siła zbrojny ukraina poinformować że południe kraj obwodz chersoński zneutralizować sześć rosyjski system obrona powietrzny ukraiński armia ocenić że niszczyć system jeden decyduć czynnik walka rosyjski lotnictwo potencjało powietrzny agresor kijowy jakub bawołek pap</t>
+          <t>Ukraińska kontrofensywa przebiega wolniej, niż zakładano, ale rozwija się zgodnie z planem - powiedział minister obrony Ukrainy Ołeksij Reznikow, cytowany w poniedziałek przez ukraińską agencję UNIAN. Polityk zapewnił, że "nie martwi się rozwojem sytuacji na froncie" ponieważ błędem jest zakładanie, że "każda ofensywa musi być błyskawiczna".
+Reznikow zaznaczył, że czynnikami spowalniającymi ataki Ukraińców są: brak amunicji, szczególnie artyleryjskiej, samych systemów artyleryjskich oraz problem obrony powietrznej.
+"Mamy bardzo długie linie frontu i wielu wrogów stojących nam na drodze. Dla nas najważniejsze pozostaje życie ukraińskich żołnierzy" - powiedział minister obrony Ukrainy.
+Reznikow zwrócił też uwagę na problem zaminowania rosyjskich pozycji obronnych. "Musimy bardzo ostrożnie używać naszych saperów" - przyznał.
+W poniedziałek siły zbrojne Ukrainy poinformowały, że na południu kraju - w obwodzie chersońskim - zneutralizowano sześć rosyjskich systemów obrony powietrznej.
+Ukraińska armia oceniła, że niszczenie tych systemów jest jednym z decydujących czynników w walce z rosyjskim lotnictwem i potencjałem powietrznym agresora.
+Z Kijowa Jakub Bawołek (PAP)
+jbw/ kb/</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>według nowy dane który poniedziałek przedstawić wiceminister obrona ukraina Hanna malar ciąg trzy tydzień działanie ofensywny armia ukraiński wyzwolić terytorium łączny powierzchnia 130 km2 suma ukraińk odzyskać kontrola dziewięciomi miejscowościa obwód doniecki zaporoski prezydent ukraina wołodymyr zełenski powiedzieć ubiegły tydzień że postęp przeciwko siła rosyjski być wolny niż oczekiwać być naciskać on przyspieszyć tłumaczyć kontrofensywa komplikować fakt zaminować rosjanin obszar około 200 tysiąc km2 kolejny głos ukraina dot problem związać Kontrofensywą Reznikow grać komputerowy również minister obrona ukraina ołeksij Reznikow przyznawać że postęp front być mało spektakularny niż początkowo zakładać jednocześnie zapewnić że martwić się rozwój sytuacja front ponieważ błąd zakładać że każdy ofensywa być błyskawiczny minister rozmowa cnn przekazać że postęp ukraiński armia spowalniać brak amunicja system artyleryjski problem obrona powietrzny kwestia obrona powietrzny chodzić że mieć też długi linia pole bitwa mieć przeciwko duży liczba wróg więc wojna grać komputerowy tłumaczyć jednocześnie wskazać że duży problem być pole minowy porozstawiać rosjanin który rozbrajać czasłochłonny siła ukraiński musieć uciekać się ręczny oczyszczać droga żołnierz pojazd pole powiedzieć reznikow dodać prawdziwy ogląd sytuacja mieć jedynie dowódca żołnierz raz musieć powtórzyć że główny wartość życie żołnierz stwierdzić wojna ukrainie osw sytuacja front według ośrodek studia wschodni siła ukraiński kontynuować ostatni dzień działanie ofensywny obwod zaporoski zachodni część obwód doniecki 24 czerwiec południe orichiwu ponownie odepchnąć rosjanin droga zbliżyć się pierwszy rosyjski umocnienie wieś robotyny następny dzień zintensyfikować natarcie południowy zachód wełyki nowosiłka atakuć kierunek pryjutn riwnopilać obwodz doniecki czytać raport osw zwracać również uwaga że ukraińcom udać się utworzyć przyczółek lewy brzeg dniepru wylot most antoniwskiy podejmować siła rosyjski próba wyparcie obrońca przynieść rezultat czytać też kontrofensywa móc utknąć amerykański prasa podawać powodyczytaj też drać bandera Miedwiediew chcieć zmiana rosyjski taktyceczytaj też naprawa czołg ukraina Polska niemiec dojść porozumienie</t>
+          <t>Według najnowszych danych, które w poniedziałek przedstawiła wiceminister obrony Ukrainy Hanna Malar, w ciągu trzech tygodni działań ofensywnych armia ukraińska wyzwoliła terytorium o łącznej powierzchni 130 km2. W sumie Ukraińcy odzyskali kontrolę nad dziewięcioma miejscowościami w obwodach donieckim i zaporoskim.
+Prezydent Ukrainy Wołodymyr Zełenski powiedział w ubiegłym tygodniu, że postępy przeciwko siłom rosyjskim są "wolniejsze niż oczekiwano", ale nie będzie naciskał, by ją przyspieszyć. Jak tłumaczył, kontrofensywę komplikuje m.in. fakt zaminowania przez Rosjan obszaru około 200 tys. km2. To kolejny głos z Ukrainy dot. problemów związanych z kontrofensywą.
+Reznikow: To nie gra komputerowa
+Również minister obrony Ukrainy Ołeksij Reznikow przyznaje, że postępy na froncie są mniej spektakularne, niż to początkowo zakładano. Jednocześnie zapewnił jednak, że "nie martwi się rozwojem sytuacji na froncie" ponieważ błędem jest zakładanie, że "każda ofensywa musi być błyskawiczna".
+Minister w rozmowie z CNN przekazał, że postępy ukraińskiej armii spowalnia brak amunicji, systemów artyleryjskich oraz problem obrony powietrznej.
+- To kwestia obrony powietrznej. Chodzi o to, że mamy też bardzo długą linię pola bitwy. I mamy przeciwko sobie dużą liczbę wrogów. Więc to jest wojna, to nie gra komputerowa - tłumaczył.
+Jednocześnie wskazał, że dużym problemem są pola minowe porozstawiane przez Rosjan, których rozbrajanie jest bardzo czasłochłonne. - Siły ukraińskie musiały uciekać się do ręcznego oczyszczania drogi dla żołnierzy i pojazdów przez pola – powiedział Reznikow.
+Jak dodał, prawdziwy ogląd sytuacji mają jedynie dowódcy i żołnierze. - I jeszcze raz muszę powtórzyć, że główną wartością dla nas jest życie naszych żołnierzy - stwierdził.
+Wojna na Ukrainie. OSW o sytuacji na froncie
+Według Ośrodka Studiów Wschodnich siły ukraińskie kontynuują w ostatnich dniach działania ofensywne w obwodzie zaporoskim i w zachodniej części obwodu donieckiego.
+"24 czerwca na południe od Orichiwu ponownie odepchnęły Rosjan od drogi Zaporoże–Mariupol i zbliżyły się do pierwszych rosyjskich umocnień we wsi Robotyne. Następnego dnia zintensyfikowały natarcie na południowy zachód od Wełykiej Nowosiłki, atakując w kierunku Pryjutnego i Riwnopila w obwodzie donieckim" – czytamy w raporcie.
+OSW zwraca również uwagę, że Ukraińcom udało się utworzyć przyczółek na lewym brzegu Dniepru u wylotu mostu Antoniwskiego, a podejmowane przez siły rosyjskie próby wyparcia obrońców nie przyniosły rezultatu.
+Czytaj też:
+"Kontrofensywa może utknąć". Amerykańska prasa podaje dwa powodyCzytaj też:
+"Dranie Bandery". Miedwiediew chce zmian w rosyjskiej taktyceCzytaj też:
+Naprawa czołgów dla Ukrainy. "Polska i Niemcy doszły do porozumienia"</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -516,8 +576,16 @@
       <c r="D4" t="n">
         <v>0.7186011075973511</v>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Ukraińska, Ukrainy, Ołeksij Reznikow, ukraińską, UNIAN, Reznikow, Ukraińców, ukraińskich, Ukrainy, Reznikow, rosyjskich, Ukrainy, chersońskim, rosyjskich, Ukraińska, rosyjskim, Kijowa, Jakub Bawołek, PAP</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ukrainy, Hanna Malar, ukraińska, Ukraińcy, donieckim, Ukrainy, Wołodymyr Zełenski, rosyjskim, Rosjan, Ukrainy, Reznikow, Ukrainy, Ołeksij Reznikow, CNN, ukraińskiej, Rosjan, ukraińskie, Reznikow, Ukrainie, OSW, Ośrodka Studiów Wschodnich, ukraińskie, donieckiego, 24 czerwca, Orichiwu, Rosjan, Zaporoże, Mariupol, rosyjskich, Robotyne, Wełykiej Nowosiłki, Pryjutnego, Riwnopila, donieckim, OSW, Ukraińcom, Dniepru, mostu, Antoniwskiego, rosyjskie, Amerykańska, Bandery, Miedwiediew, rosyjskiej, Ukrainy, Polska, Niemcy</t>
+        </is>
+      </c>
       <c r="G4" t="n">
         <v>0.108695652173913</v>
       </c>
@@ -525,12 +593,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ukraiński kontrofensywa przebiegać wolniej niż zakładać rozwijać się zgodnie plan powiedzieć minister obrona ukraina ołeksij reznikow cytować poniedziałek ukraiński agencja unianin polityk zapewnić że martwić się rozwój sytuacja front ponieważ błąd zakładać że każdy ofensywa być błyskawiczny reznikow zaznaczyć że czynnik spowalniający atak ukraińca być brak amunicja szczególnie artyleryjski sam system artyleryjski problem obrona powietrzny mieć długi linia front wróg stać droga ważny pozostawać życie ukraiński żołnierz powiedzieć minister obrona ukraina Reznikow zwrócić też uwaga problem zaminować rosyjski pozycja obronny musieć ostrożnie używać saper przyznać poniedziałek siła zbrojny ukraina poinformować że południe kraj obwodz chersoński zneutralizować sześć rosyjski system obrona powietrzny ukraiński armia ocenić że niszczyć system jeden decyduć czynnik walka rosyjski lotnictwo potencjało powietrzny agresor kijowy jakub bawołek pap</t>
+          <t>Ukraińska kontrofensywa przebiega wolniej, niż zakładano, ale rozwija się zgodnie z planem - powiedział minister obrony Ukrainy Ołeksij Reznikow, cytowany w poniedziałek przez ukraińską agencję UNIAN. Polityk zapewnił, że "nie martwi się rozwojem sytuacji na froncie" ponieważ błędem jest zakładanie, że "każda ofensywa musi być błyskawiczna".
+Reznikow zaznaczył, że czynnikami spowalniającymi ataki Ukraińców są: brak amunicji, szczególnie artyleryjskiej, samych systemów artyleryjskich oraz problem obrony powietrznej.
+"Mamy bardzo długie linie frontu i wielu wrogów stojących nam na drodze. Dla nas najważniejsze pozostaje życie ukraińskich żołnierzy" - powiedział minister obrony Ukrainy.
+Reznikow zwrócił też uwagę na problem zaminowania rosyjskich pozycji obronnych. "Musimy bardzo ostrożnie używać naszych saperów" - przyznał.
+W poniedziałek siły zbrojne Ukrainy poinformowały, że na południu kraju - w obwodzie chersońskim - zneutralizowano sześć rosyjskich systemów obrony powietrznej.
+Ukraińska armia oceniła, że niszczenie tych systemów jest jednym z decydujących czynników w walce z rosyjskim lotnictwem i potencjałem powietrznym agresora.
+Z Kijowa Jakub Bawołek (PAP)
+jbw/ kb/</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ukraiński kontrofensywa przebiegać wolniej niż zakładać rozwijać się zgodnie plan powiedzieć minister obrona ukraina ołeksij reznikow cytować poniedziałek ukraiński agencja unianin polityk zapewnić że martwić się rozwój sytuacja front ponieważ błąd zakładać że każdy ofensywa być błyskawiczny reznikow zaznaczyć że czynnik spowalniający atak ukraińca być brak amunicja szczególnie artyleryjski sam system artyleryjski problem obrona powietrzny mieć długi linia front wróg stać droga ważny pozostawać życie ukraiński żołnierz powiedzieć minister obrona ukraina Reznikow zwrócić też uwaga problem zaminować rosyjski pozycja obronny musieć ostrożnie używać saper przyznać czytać też żaryn bunt prigożyna napełnić rosjanin obawami koniec twitter robić musk poniedziałek siła zbrojny ukraina poinformować że południe kraj obwodz chersoński zneutralizować sześć rosyjski system obrona powietrzny ukraiński armia ocenić że niszczyć system jeden decyduć czynnik walka rosyjski lotnictwo potencjało powietrzny agresor kijowy jakub bawołek</t>
+          <t>Ukraińska kontrofensywa przebiega wolniej, niż zakładano, ale rozwija się zgodnie z planem - powiedział minister obrony Ukrainy Ołeksij Reznikow, cytowany w poniedziałek przez ukraińską agencję UNIAN.
+Polityk zapewnił, że „nie martwi się rozwojem sytuacji na froncie” ponieważ błędem jest zakładanie, że „każda ofensywa musi być błyskawiczna”.
+Reznikow zaznaczył, że czynnikami spowalniającymi ataki Ukraińców są: brak amunicji, szczególnie artyleryjskiej, samych systemów artyleryjskich oraz problem obrony powietrznej.
+„Mamy bardzo długie linie frontu i wielu wrogów stojących nam na drodze. Dla nas najważniejsze pozostaje życie ukraińskich żołnierzy” - powiedział minister obrony Ukrainy.
+Reznikow zwrócił też uwagę na problem zaminowania rosyjskich pozycji obronnych. „Musimy bardzo ostrożnie używać naszych saperów” - przyznał.
+CZYTAJ TEŻ:
+Żaryn: bunt Prigożyna napełnił Rosjan obawami
+To koniec Twittera! Co robi Musk?
+W poniedziałek siły zbrojne Ukrainy poinformowały, że na południu kraju - w obwodzie chersońskim - zneutralizowano sześć rosyjskich systemów obrony powietrznej.
+Ukraińska armia oceniła, że niszczenie tych systemów jest jednym z decydujących czynników w walce z rosyjskim lotnictwem i potencjałem powietrznym agresora.
+Z Kijowa Jakub Bawołek
+PAP/ as/</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -539,8 +625,16 @@
       <c r="D5" t="n">
         <v>0.9997757077217102</v>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Ukraińska, Ukrainy, Ołeksij Reznikow, ukraińską, UNIAN, Reznikow, Ukraińców, ukraińskich, Ukrainy, Reznikow, rosyjskich, Ukrainy, chersońskim, rosyjskich, Ukraińska, rosyjskim, Kijowa, Jakub Bawołek, PAP</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ukraińska, Ukrainy, Ołeksij Reznikow, ukraińską, UNIAN, Reznikow, Ukraińców, ukraińskich, Ukrainy, Reznikow, rosyjskich, Żaryn, Prigożyna, Rosjan, Musk, Ukrainy, chersońskim, rosyjskich, Ukraińska, rosyjskim, Kijowa, Jakub Bawołek</t>
+        </is>
+      </c>
       <c r="G5" t="n">
         <v>0.7222222222222222</v>
       </c>
@@ -548,12 +642,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ukraiński kontrofensywa przebiegać wolniej niż zakładać rozwijać się zgodnie plan powiedzieć minister obrona ukraina ołeksij reznikow cytować poniedziałek ukraiński agencja unianin polityk zapewnić że martwić się rozwój sytuacja front ponieważ błąd zakładać że każdy ofensywa być błyskawiczny reznikow zaznaczyć że czynnik spowalniający atak ukraińca być brak amunicja szczególnie artyleryjski sam system artyleryjski problem obrona powietrzny mieć długi linia front wróg stać droga ważny pozostawać życie ukraiński żołnierz powiedzieć minister obrona ukraina Reznikow zwrócić też uwaga problem zaminować rosyjski pozycja obronny musieć ostrożnie używać saper przyznać poniedziałek siła zbrojny ukraina poinformować że południe kraj obwodz chersoński zneutralizować sześć rosyjski system obrona powietrzny ukraiński armia ocenić że niszczyć system jeden decyduć czynnik walka rosyjski lotnictwo potencjało powietrzny agresor kijowy jakub bawołek pap</t>
+          <t>Ukraińska kontrofensywa przebiega wolniej, niż zakładano, ale rozwija się zgodnie z planem - powiedział minister obrony Ukrainy Ołeksij Reznikow, cytowany w poniedziałek przez ukraińską agencję UNIAN. Polityk zapewnił, że "nie martwi się rozwojem sytuacji na froncie" ponieważ błędem jest zakładanie, że "każda ofensywa musi być błyskawiczna".
+Reznikow zaznaczył, że czynnikami spowalniającymi ataki Ukraińców są: brak amunicji, szczególnie artyleryjskiej, samych systemów artyleryjskich oraz problem obrony powietrznej.
+"Mamy bardzo długie linie frontu i wielu wrogów stojących nam na drodze. Dla nas najważniejsze pozostaje życie ukraińskich żołnierzy" - powiedział minister obrony Ukrainy.
+Reznikow zwrócił też uwagę na problem zaminowania rosyjskich pozycji obronnych. "Musimy bardzo ostrożnie używać naszych saperów" - przyznał.
+W poniedziałek siły zbrojne Ukrainy poinformowały, że na południu kraju - w obwodzie chersońskim - zneutralizowano sześć rosyjskich systemów obrony powietrznej.
+Ukraińska armia oceniła, że niszczenie tych systemów jest jednym z decydujących czynników w walce z rosyjskim lotnictwem i potencjałem powietrznym agresora.
+Z Kijowa Jakub Bawołek (PAP)
+jbw/ kb/</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>noc rosjanin ponownie bombardować ukraiński miasto alarm przeciwlotniczy ogłoszić kijowie który zbliżać się dron według lokalny media udać się zestrzelić syrena alarmowy słychać być również obwodzie odeski tarnopolski chmielnicki rówieński ukraiński oddział odeprzeć seria szturm łyman bachmut awdijiwką według dane sztab ukrainiec powoli posuwać się naprzód okolica melitopola berdiański obwoda zaporoski ukraiński kontrofensywa opóźnić przebiegać zgodnie plan zapewniać minister obrona ukraina ołeksij Reznikow wymienić długi linia front duży liczba wrogi rosyjski żołnierz rozległy pole minowy pozostawić rosyjski armia który niejednokrotnie musieć być rozminowywać ręcznie tworzyć korytarz wojsko prowadzący kontrofensywa wojna grać komputerowy tłumaczyć ukraiński minister obrona</t>
+          <t>W nocy Rosjanie ponownie bombardowali ukraińskie miasta. Alarm przeciwlotniczy ogłoszono w Kijowie, do którego zbliżały się drony.
+Według lokalnych mediów udało się je zestrzelić. Syreny alarmowe słychać było również w obwodzie odeskim, tarnopolskim, chmielnickim i rówieńskim.
+Ukraińskie oddziały odparły serię szturmów od Łymanem, Bachmutem i Awdijiwką. Według danych sztabu, Ukraińcy powoli posuwają się naprzód w okolicy Melitopola i Berdiańska w obwodzie zaporoskim.
+Ukraińska kontrofensywa jest opóźniona, ale przebiega zgodnie z planem - zapewnia minister obrony Ukrainy Ołeksij Reznikow. Wymienił długą linię frontu, dużą liczbę wrogich rosyjskich żołnierzy oraz rozległe pola minowe pozostawione przez rosyjską armię, które niejednokrotnie muszą być rozminowywane ręcznie tworząc korytarze dla wojska prowadzącego kontrofensywę. - To wojna, a nie gra komputerowa - tłumaczy ukraiński minister obrony.</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -562,8 +666,16 @@
       <c r="D6" t="n">
         <v>0.6871125102043152</v>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Ukraińska, Ukrainy, Ołeksij Reznikow, ukraińską, UNIAN, Reznikow, Ukraińców, ukraińskich, Ukrainy, Reznikow, rosyjskich, Ukrainy, chersońskim, rosyjskich, Ukraińska, rosyjskim, Kijowa, Jakub Bawołek, PAP</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rosjanie, ukraińskie, Kijowie, odeskim, tarnopolskim, chmielnickim, rówieńskim, Ukraińskie, Łymanem, Bachmutem, Awdijiwką, Ukraińcy, Melitopola, Berdiańska, Ukraińska, Ukrainy, Ołeksij Reznikow, rosyjskich, rosyjską, ukraiński</t>
+        </is>
+      </c>
       <c r="G6" t="n">
         <v>0.1333333333333333</v>
       </c>
@@ -571,12 +683,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ukraiński kontrofensywa przebiegać wolniej niż zakładać rozwijać się zgodnie plan powiedzieć minister obrona ukraina ołeksij reznikow cytować poniedziałek ukraiński agencja unianin polityk zapewnić że martwić się rozwój sytuacja front ponieważ błąd zakładać że każdy ofensywa być błyskawiczny reznikow zaznaczyć że czynnik spowalniający atak ukraińca być brak amunicja szczególnie artyleryjski sam system artyleryjski problem obrona powietrzny mieć długi linia front wróg stać droga ważny pozostawać życie ukraiński żołnierz powiedzieć minister obrona ukraina Reznikow zwrócić też uwaga problem zaminować rosyjski pozycja obronny musieć ostrożnie używać saper przyznać poniedziałek siła zbrojny ukraina poinformować że południe kraj obwodz chersoński zneutralizować sześć rosyjski system obrona powietrzny ukraiński armia ocenić że niszczyć system jeden decyduć czynnik walka rosyjski lotnictwo potencjało powietrzny agresor kijowy jakub bawołek pap</t>
+          <t>Ukraińska kontrofensywa przebiega wolniej, niż zakładano, ale rozwija się zgodnie z planem - powiedział minister obrony Ukrainy Ołeksij Reznikow, cytowany w poniedziałek przez ukraińską agencję UNIAN. Polityk zapewnił, że "nie martwi się rozwojem sytuacji na froncie" ponieważ błędem jest zakładanie, że "każda ofensywa musi być błyskawiczna".
+Reznikow zaznaczył, że czynnikami spowalniającymi ataki Ukraińców są: brak amunicji, szczególnie artyleryjskiej, samych systemów artyleryjskich oraz problem obrony powietrznej.
+"Mamy bardzo długie linie frontu i wielu wrogów stojących nam na drodze. Dla nas najważniejsze pozostaje życie ukraińskich żołnierzy" - powiedział minister obrony Ukrainy.
+Reznikow zwrócił też uwagę na problem zaminowania rosyjskich pozycji obronnych. "Musimy bardzo ostrożnie używać naszych saperów" - przyznał.
+W poniedziałek siły zbrojne Ukrainy poinformowały, że na południu kraju - w obwodzie chersońskim - zneutralizowano sześć rosyjskich systemów obrony powietrznej.
+Ukraińska armia oceniła, że niszczenie tych systemów jest jednym z decydujących czynników w walce z rosyjskim lotnictwem i potencjałem powietrznym agresora.
+Z Kijowa Jakub Bawołek (PAP)
+jbw/ kb/</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ukraiński kontrofensywa przebiegać wolniej niż zakładać rozwijać się zgodnie plan powiedzieć minister obrona ukraina ołeksij reznikow cytować ukraiński agencja unianin polityk zapewnić że martwić się rozwój sytuacja front ponieważ błąd zakładać że każdy ofensywa być błyskawiczny reznikow zaznaczyć że czynnik spowalniający atak ukraińca być brak amunicja szczególnie artyleryjski sam system artyleryjski problem obrona powietrzny mieć długi linia front wróg stać droga ważny pozostawać życie ukraiński żołnierz powiedzieć minister obrona ukraina wieszwiecej polubić Reznikow zwrócić też uwaga problem zaminować rosyjski pozycja obronny musieć ostrożnie używać saper przyznać poniedziałek siła zbrojny ukraina poinformować że południe kraj obwodz chersoński zneutralizować sześć rosyjski system obrona powietrzny ukraiński armia ocenić że niszczyć system jeden decyduć czynnik walka rosyjski lotnictwo potencjało powietrzny agresor</t>
+          <t xml:space="preserve">Ukraińska kontrofensywa przebiega wolniej, niż zakładano, ale rozwija się zgodnie z planem – powiedział minister obrony Ukrainy Ołeksij Reznikow, cytowany przez ukraińską agencję UNIAN.
+Polityk zapewnił, że „nie martwi się rozwojem sytuacji na froncie” ponieważ błędem jest zakładanie, że „każda ofensywa musi być błyskawiczna”.
+Reznikow zaznaczył, że czynnikami spowalniającymi ataki Ukraińców są: brak amunicji, szczególnie artyleryjskiej, samych systemów artyleryjskich oraz problem obrony powietrznej.
+– Mamy bardzo długie linie frontu i wielu wrogów stojących nam na drodze. Dla nas najważniejsze pozostaje życie ukraińskich żołnierzy – powiedział minister obrony Ukrainy.
+#wieszwiecej Polub nas
+Reznikow zwrócił też uwagę na problem zaminowania rosyjskich pozycji obronnych. – Musimy bardzo ostrożnie używać naszych saperów – przyznał.
+W poniedziałek Siły Zbrojne Ukrainy poinformowały, że na południu kraju – w obwodzie chersońskim – zneutralizowano sześć rosyjskich systemów obrony powietrznej. Ukraińska armia oceniła, że niszczenie tych systemów jest jednym z decydujących czynników w walce z rosyjskim lotnictwem i potencjałem powietrznym agresora.
+</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -585,8 +711,16 @@
       <c r="D7" t="n">
         <v>0.9924001693725586</v>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Ukraińska, Ukrainy, Ołeksij Reznikow, ukraińską, UNIAN, Reznikow, Ukraińców, ukraińskich, Ukrainy, Reznikow, rosyjskich, Ukrainy, chersońskim, rosyjskich, Ukraińska, rosyjskim, Kijowa, Jakub Bawołek, PAP</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ukraińska, Ukrainy, Ołeksij Reznikow, ukraińską, UNIAN, Reznikow, Ukraińców, ukraińskich, Ukrainy, Reznikow, rosyjskich, Siły Zbrojne Ukrainy, chersońskim, rosyjskich, Ukraińska, rosyjskim</t>
+        </is>
+      </c>
       <c r="G7" t="n">
         <v>0.7333333333333333</v>
       </c>
@@ -594,12 +728,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ukraiński kontrofensywa przebiegać wolniej niż zakładać rozwijać się zgodnie plan powiedzieć minister obrona ukraina ołeksij reznikow cytować poniedziałek ukraiński agencja unianin polityk zapewnić że martwić się rozwój sytuacja front ponieważ błąd zakładać że każdy ofensywa być błyskawiczny reznikow zaznaczyć że czynnik spowalniający atak ukraińca być brak amunicja szczególnie artyleryjski sam system artyleryjski problem obrona powietrzny mieć długi linia front wróg stać droga ważny pozostawać życie ukraiński żołnierz powiedzieć minister obrona ukraina Reznikow zwrócić też uwaga problem zaminować rosyjski pozycja obronny musieć ostrożnie używać saper przyznać poniedziałek siła zbrojny ukraina poinformować że południe kraj obwodz chersoński zneutralizować sześć rosyjski system obrona powietrzny ukraiński armia ocenić że niszczyć system jeden decyduć czynnik walka rosyjski lotnictwo potencjało powietrzny agresor kijowy jakub bawołek pap</t>
+          <t>Ukraińska kontrofensywa przebiega wolniej, niż zakładano, ale rozwija się zgodnie z planem - powiedział minister obrony Ukrainy Ołeksij Reznikow, cytowany w poniedziałek przez ukraińską agencję UNIAN. Polityk zapewnił, że "nie martwi się rozwojem sytuacji na froncie" ponieważ błędem jest zakładanie, że "każda ofensywa musi być błyskawiczna".
+Reznikow zaznaczył, że czynnikami spowalniającymi ataki Ukraińców są: brak amunicji, szczególnie artyleryjskiej, samych systemów artyleryjskich oraz problem obrony powietrznej.
+"Mamy bardzo długie linie frontu i wielu wrogów stojących nam na drodze. Dla nas najważniejsze pozostaje życie ukraińskich żołnierzy" - powiedział minister obrony Ukrainy.
+Reznikow zwrócił też uwagę na problem zaminowania rosyjskich pozycji obronnych. "Musimy bardzo ostrożnie używać naszych saperów" - przyznał.
+W poniedziałek siły zbrojne Ukrainy poinformowały, że na południu kraju - w obwodzie chersońskim - zneutralizowano sześć rosyjskich systemów obrony powietrznej.
+Ukraińska armia oceniła, że niszczenie tych systemów jest jednym z decydujących czynników w walce z rosyjskim lotnictwem i potencjałem powietrznym agresora.
+Z Kijowa Jakub Bawołek (PAP)
+jbw/ kb/</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>początek czerwiec rozpocząć się zapowiadać miesiąc kontrofensywa ukraina ukraińcy wyzwolić wieś staromajorski czwartkowy wieczór 27 lipiec ukraiński agencja prasowy unian poinformować kolejny postęp front spod okupacja rosjanin wyzwolono miejscowość staromajorski obwodzie doniecki krok blisko przełamać główny linia obrona chwała narod skomentować telegram ukraiński analityk do spraw wojskowość ołeksandr kowalenko twitter rosjanin ufortyfikować pozycja słowo kowalenka przypominać że kontrofensywa ukraina przebiegać dotychczas taki tempo oczekiwać wynikać fakt że rosjanin solidnie ufortyfikować pozycja okupować teren szerokość pas rosyjski zasiek row przeciwczołgowy pole minowy sięgać miejsce 30 kilometr ogromny znaczenie również że najeźdźcy mieć przewaga powietrzny ukraiński dowództwo podkreślać że starać się oszczędzać życie swój żołnierz wydawać samobójczy rozkazów ukraiński kontrofensywa przebiegać wolniej niż zakładać rozwijać się zgodnie plan wojna grać komputerowy główny wartość życie żołnierz tłumaczyć niedawno rozmowa amerykański telewizja cnn ołeksij reznikow szef resort obrona ukraina jednostka rezerwowy przybyły wykorzystać okazja nowy ustalenie cnn wynikać że ukraiński kontrofensywa właśnie nabierać rozpąd kij skierować właśnie front dodatkowy żołnierz pokłos fakt że ukraińcom udać się niektóry miejsce przebić przejście rosyjski umocnienie pole minowy ukraina wydawać się eskalować kontrofensywa zwiększać rozmieścić dodatkowy żołnierz front południowy kij zidentyfikować potencjalny słabość rosyjski linia obronny kontrofensywa przeedrzeć się niektóry element rosyjski linia obronny południowy wschód jednostka rezerwowy przybyły wykorzystać okazja donosić cnn podstawa rozmowa amerykański urzędnik sekretarz obrona usa lloyd austin skomentować status ukraiński kontrofensywa trakt wizyta papuić który mieć miejsce czwartek 27 lipiec austin podkreślić że ukraina przygotować wyszkolyć odnieść sukces czytać też łukaszenk Putin dążyć destabilizacja Polska le figaro winąć dud zełenskiegoczytaj też trwać tajny rozmowa między amerykan rosjana wykorzystać ścieżka</t>
+          <t>Na początku czerwca rozpoczęła się zapowiadana od wielu miesięcy kontrofensywa Ukrainy.
+Ukraińcy wyzwolili wieś Staromajorskie
+W czwartkowy wieczór, 27 lipca, ukraińska agencja prasowa UNIAN poinformowała o kolejnym postępie na froncie – spod okupacji Rosjan wyzwolono miejscowość Staromajorskie w obwodzie donieckim.
+„O krok bliżej do przełamania głównej linii obrony. Chwała narodowi!” – skomentował na Telegramie ukraiński analityk ds. wojskowości Ołeksandr Kowalenko.
+twitter
+Rosjanie ufortyfikowali swoje pozycje
+Słowa Kowalenki przypominają, że kontrofensywa Ukrainy nie przebiegała dotychczas w takim tempie, jak oczekiwano. Wynika to z faktu, że Rosjanie solidnie ufortyfikowali swoje pozycje na okupowanych terenach.
+Szerokość pasa rosyjskich zasieków, rowów przeciwczołgowych czy pól minowych sięga miejscami nawet 30 km. Ogromne znaczenie ma również to, że najeźdźcy mają przewagę powietrzną.
+Ukraińskie dowództwo podkreśla, że stara się oszczędzać życie swoich żołnierzy i nie wydawać im samobójczych rozkazów.
+– Ukraińska kontrofensywa przebiega wolniej, niż zakładano, ale rozwija się zgodnie z planem (...) To jest wojna, to nie gra komputerowa (...) główną wartością dla nas jest życie naszych żołnierzy – tłumaczył niedawno w rozmowie z amerykańską telewizją CNN Ołeksij Reznikow, szef resortu obrony Ukrainy.
+„Jednostki rezerwowe przybyły, aby wykorzystać okazję”
+Jednak z najnowszych ustaleń CNN wynika, że ukraińska kontrofensywa właśnie nabiera rozpędu. Kijów skierował właśnie na front dodatkowych żołnierzy.
+To pokłosie faktu, że Ukraińcom udało się w niektórych miejscach przebić przejścia przez rosyjskie umocnienia, przede wszystkim przez pola minowe.
+„Ukraina wydaje się eskalować kontrofensywę, zwiększając rozmieszczenie dodatkowych żołnierzy na froncie południowym (...) Kijów zidentyfikował potencjalne słabości rosyjskich linii obronnych (...) Kontrofensywa przedarła się przez niektóre elementy rosyjskich linii obronnych na południowym wschodzie, a jednostki rezerwowe przybyły, aby wykorzystać okazję” – donosi CNN na podstawie rozmów z amerykańskimi urzędnikami.
+Sekretarz obrony USA Lloyd Austin nie skomentował statusu ukraińskiej kontrofensywy. Jednak w trakcie wizyty w Papui Nowej-Gwinei – która miała miejsce w czwartek, 27 lipca – Austin podkreślił, że „Ukraina jest dobrze przygotowana i dobrze wyszkolona, aby odnieść sukces”.
+Czytaj też:
+Łukaszenka i Putin dążą do destabilizacji Polski? Le Figaro o „winie” Dudy i ZełenskiegoCzytaj też:
+Trwają tajne rozmowy między Amerykanami i Rosjanami. Wykorzystano „ścieżkę 1,5”</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -608,8 +766,16 @@
       <c r="D8" t="n">
         <v>0.6747000813484192</v>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Ukraińska, Ukrainy, Ołeksij Reznikow, ukraińską, UNIAN, Reznikow, Ukraińców, ukraińskich, Ukrainy, Reznikow, rosyjskich, Ukrainy, chersońskim, rosyjskich, Ukraińska, rosyjskim, Kijowa, Jakub Bawołek, PAP</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>czerwca, Ukrainy, Ukraińcy, Staromajorskie, 27 lipca, ukraińska, UNIAN, Rosjan, Staromajorskie, donieckim, ukraiński, Ołeksandr Kowalenko, Rosjanie, Kowalenki, Ukrainy, Rosjanie, rosyjskich, Ukraińskie, Ukraińska, amerykańską, CNN, Ołeksij Reznikow, Ukrainy, CNN, ukraińska, Kijów, Ukraińcom, rosyjskie, Ukraina, Kijów, rosyjskich, rosyjskich, CNN, amerykańskimi, USA, Lloyd Austin, ukraińskiej, Papui Nowej, Gwinei, 27 lipca, Austin, Ukraina, Łukaszenka, Putin, Polski, Le Figaro, Dudy, Amerykanami, Rosjanami</t>
+        </is>
+      </c>
       <c r="G8" t="n">
         <v>0.108695652173913</v>
       </c>
@@ -617,12 +783,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ukraiński kontrofensywa przebiegać wolniej niż zakładać rozwijać się zgodnie plan powiedzieć minister obrona ukraina ołeksij reznikow cytować poniedziałek ukraiński agencja unianin polityk zapewnić że martwić się rozwój sytuacja front ponieważ błąd zakładać że każdy ofensywa być błyskawiczny reznikow zaznaczyć że czynnik spowalniający atak ukraińca być brak amunicja szczególnie artyleryjski sam system artyleryjski problem obrona powietrzny mieć długi linia front wróg stać droga ważny pozostawać życie ukraiński żołnierz powiedzieć minister obrona ukraina Reznikow zwrócić też uwaga problem zaminować rosyjski pozycja obronny musieć ostrożnie używać saper przyznać poniedziałek siła zbrojny ukraina poinformować że południe kraj obwodz chersoński zneutralizować sześć rosyjski system obrona powietrzny ukraiński armia ocenić że niszczyć system jeden decyduć czynnik walka rosyjski lotnictwo potencjało powietrzny agresor kijowy jakub bawołek pap</t>
+          <t>Ukraińska kontrofensywa przebiega wolniej, niż zakładano, ale rozwija się zgodnie z planem - powiedział minister obrony Ukrainy Ołeksij Reznikow, cytowany w poniedziałek przez ukraińską agencję UNIAN. Polityk zapewnił, że "nie martwi się rozwojem sytuacji na froncie" ponieważ błędem jest zakładanie, że "każda ofensywa musi być błyskawiczna".
+Reznikow zaznaczył, że czynnikami spowalniającymi ataki Ukraińców są: brak amunicji, szczególnie artyleryjskiej, samych systemów artyleryjskich oraz problem obrony powietrznej.
+"Mamy bardzo długie linie frontu i wielu wrogów stojących nam na drodze. Dla nas najważniejsze pozostaje życie ukraińskich żołnierzy" - powiedział minister obrony Ukrainy.
+Reznikow zwrócił też uwagę na problem zaminowania rosyjskich pozycji obronnych. "Musimy bardzo ostrożnie używać naszych saperów" - przyznał.
+W poniedziałek siły zbrojne Ukrainy poinformowały, że na południu kraju - w obwodzie chersońskim - zneutralizowano sześć rosyjskich systemów obrony powietrznej.
+Ukraińska armia oceniła, że niszczenie tych systemów jest jednym z decydujących czynników w walce z rosyjskim lotnictwem i potencjałem powietrznym agresora.
+Z Kijowa Jakub Bawołek (PAP)
+jbw/ kb/</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>musieć ostrożnie podchodzić tematyka inflacja jakimiś ruch który mieć pomóc rząd niż obywatel niż podmiot gospodarczy doprowadzić odwrócyć obecny trend powiedzieć program antena tvn24 członek rada polityka pieniężny przemysław litwiniuk program antena tvn24 przemysław litwiniuk mówić stać się jeżeli dojść ewentualny obniżka stopa procentowy molo wydawać się bardzo wiarygodny miejsce objawienie jeżeli chodzić kierunek polityka pieniężny obserwywać już wypowiedź rada który rodzaj komunikacja wyinterpretowaniać mniej wprost mówić rodzaj ruch niejako przewrócić stolik założenie projekcja lipcowy być musieć dopiero poczekać projekcja listopadowy zobaczyć być mieć konsekwencja dodać stwierdzić że mieć więcej ryzyko utrzymać przebieg ścieżka dezinflacja niż szansa że stać się optymistyczny scenariusz musieć ostrożnie podchodzić tematyka inflacja jakimiś ruch który mieć pomóc rząd niż obywatel niż podmiot gospodarczy doprowadzić odwrócenie trend powiedzieć Przemysław litwiniuk materiał część serwis tvn24 autor źródło tvn24</t>
+          <t>Musimy bardzo ostrożnie podchodzić do tematyki inflacji, aby jakimiś ruchami, które mają bardziej pomóc rządowi niż obywatelom, niż podmiotom gospodarczym, nie doprowadzić do odwrócenia obecnego trendu - powiedział w programie "Jeden na Jeden" na antenie TVN24 członek Rady Polityki Pieniężnej prof. Przemysław Litwiniuk.
+W programie "Jeden na jeden" na antenie TVN24 prof. Przemysław Litwiniuk mówił, co stanie się, jeżeli w tym roku dojdzie do ewentualnej obniżki stóp procentowych.
+- Molo wydaje się najbardziej wiarygodnym miejscem objawień, jeżeli chodzi o kierunek polityki pieniężnej. Obserwujemy jednak już kilka wypowiedzi z Rady, w których tego rodzaju komunikacja jest do wyinterpretowania bardziej lub mniej wprost - mówił.
+- Tego rodzaju ruch niejako przewróci stolik w tych założeniach projekcji lipcowej. Będziemy musieli dopiero poczekać na projekcję listopadową, aby zobaczyć, jakie to będzie miało konsekwencje - dodał.
+Stwierdził jednak, że "dzisiaj mamy więcej ryzyk dla utrzymania przebiegu tej ścieżki dezinflacji niż szans, że stanie się to w bardziej optymistycznym scenariuszu".
+- Musimy bardzo ostrożnie podchodzić do tematyki inflacji, aby jakimiś ruchami, które mają bardziej pomóc rządowi niż obywatelom, niż podmiotom gospodarczym, nie doprowadzić do odwrócenia tego trendu - powiedział.
+Prof. Przemysław Litwiniuk w "Jeden na jeden" Materiał jest częścią serwisu TVN24 GO
+Autor:mp/ams
+Źródło: TVN24</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -631,8 +812,16 @@
       <c r="D9" t="n">
         <v>0.3459644317626953</v>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ukraińska, Ukrainy, Ołeksij Reznikow, ukraińską, UNIAN, Reznikow, Ukraińców, ukraińskich, Ukrainy, Reznikow, rosyjskich, Ukrainy, chersońskim, rosyjskich, Ukraińska, rosyjskim, Kijowa, Jakub Bawołek, PAP</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>TVN24, Rady Polityki Pieniężnej, Przemysław Litwiniuk, TVN24, Przemysław Litwiniuk, Rady, Przemysław Litwiniuk, TVN24, Autor, ams, TVN24</t>
+        </is>
+      </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
@@ -640,12 +829,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>instytut meteorologia gospodarka wodny ostrzegł burz który miejsce być towarzyszyć silny opad deszcz grad poryw wiatr wysoki ostrzeżenie wydać południe kraj część województwo wielkopolski ostrzeżenie drugi stopień burza gradem wydać przeważający część województwo podkarpacki małopolski także część województwo śląski wielkopolski instytut prognozować burza który miejsce być towarzyszyć silny opad deszcz 40 mentymetr poryw wiatr 90 miejsce móc pojawić się grad pozostały część kraj wyjątek województwo podlaski opolski dolnośląski część województwo małopolski wielkopolski lubuski obowiązywać alerta pierwszy stopień imgw prognozywać burza który miejsce być towarzyszyć silny opad deszcz lokalnie 30 mentymetr poryw wiatr 80 miejsce grad wtorek północ instytut poinformować twitterz że polski obserwować być rozległy obszar występować burz pomorzu północny wielkopolsce małopolska podkarpaciu lubelszczyźna burza przemieszczać się kierunek alert pierwszy stopień oznaczać że móc wystąpić niebezpieczny zjawisko meteorologiczny który móc powodować strata materialny zagrożenie zdrowie życie ostrzeżenie drugi stopień oznaczać że zjawisko móc być zintensyfikować niebezpieczny pap autor Marcin chomiuk</t>
+          <t>Instytut Meteorologii i Gospodarki Wodnej ostrzegł przed burzami, którym miejscami będą towarzyszyć silne opady deszczu, grad oraz porywy wiatru. Najwyższe ostrzeżenia wydano dla południa kraju oraz dla części województwa wielkopolskiego. Ostrzeżenia drugiego stopnia przed burzami z gradem wydano dla przeważającej części województwa podkarpackiego i małopolskiego, a także dla części województw śląskiego i wielkopolskiego. Instytut prognozuje tam burze, którym miejscami będą towarzyszyć silne opady deszczu - do 40 mm, oraz porywy wiatru - do 90 km/h, miejscami może pojawić się grad.
+W pozostałej części kraju, z wyjątkiem województwa podlaskiego, opolskiego, dolnośląskiego i części województw warmińsko-mazurskiego, małopolskiego, wielkopolskiego i lubuskiego obowiązują alerty pierwszego stopnia. IMGW prognozuje tam burze, którym miejscami będą towarzyszyć silne opady deszczu - lokalnie do 30 mm oraz porywy wiatru do 80 km/h. Miejscami grad.
+We wtorek po północy Instytut poinformował na Twitterze, że nad Polską obserwowane są dwa rozległe obszary występowania burz: na Pomorzu i w północnej Wielkopolsce oraz w Małopolsce, na Podkarpaciu i Lubelszczyźnie. Burze przemieszczają się w kierunku północno-wschodnim.
+Alert pierwszego stopnia oznacza, że mogą wystąpić niebezpieczne zjawiska meteorologiczne, które mogą powodować straty materialne oraz zagrożenie dla zdrowia i życia. Ostrzeżenia drugiego stopnia oznaczają, że zjawiska te mogą być zintensyfikowane i bardziej niebezpieczne. (PAP)
+autor: Marcin Chomiuk
+mchom/ kb/</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>mazowiecki jedyny województwo sprawa płaca Warszawa który zarabiać się średnio powyżej 8 tysiąc złoty miesięcznie podkarpacie zaś jeden trzy który płaca być poniżej 6 tysiąc choć granica brakować kilkanaście złoty przypadek województwo świętokrzyskiy 60 złoty się dziać podkarpacie reklama wniosek płynąć czerwcowy dane gusa płac firma który pracować powyżej dziesięć osoba ciąg bardzo wzrosnąć podlasiu 17 większość region wzrost poziom proc czytać więcej wynagrodzenie rządowy podwyżka płaca 700 złoty rekord unia europejski polski płaca minimalny być najwyższa porównaniu przeciętny wynagrodzenie unia europejski przyszły firma poradzić skokowy wzrost region który przeciętnie zarabiać się powyżej tysiąc być województwo dolnośląski małopolski śląski pomorski pensja być zwykle wysoki duży miasto który koszt życie być wysoki popyt wykwalifikować specjalista duży mniejszych gospodarczo słabie rozwinięty obszar wynagrodzenie móc być niższe wynikać mniejszych koszt utrzymać mało konkurencyjny rynek praca ważny także struktura firma duży organizacja mieć duży zasób móc zatem oferować dobry warunek finansowy niż mały firma przypominać mart szymańska manpower</t>
+          <t>Mazowieckie to jedyne województwo (a i to: za sprawą płac w Warszawie), w którym zarabia się średnio powyżej 8 tys. złotych miesięcznie. Podkarpacie jest zaś jednym z trzech, w których płace są poniżej 6 tys. Choć do tej granicy brakuje w nich kilkunastu złotych – jak w przypadku województw warmińsko-mazurskiego czy świętokrzyskiego, czy 60 zł – jak to się dzieje na Podkarpaciu.
+Reklama
+Takie wnioski płyną z czerwcowych danych GUS o płacach w firmach, w których pracuje powyżej dziesięciu osób. W ciągu roku najbardziej wzrosły one na Podlasiu (o ponad 17 proc.). W większości regionów wzrost jest na poziomie 11–12 proc.
+Czytaj więcej Wynagrodzenia Rządowa podwyżka płacy o 700 złotych. Rekord w Unii Europejskiej Polska płaca minimalna będzie najwyższa w porównaniu z przeciętnym wynagrodzeniem w Unii Europejskiej w przyszłym roku. Nie wszystkie firmy poradzą sobie z jej skokowym wzrostem.
+Regionami, w których przeciętnie zarabia się powyżej 7,5 tys. są województwa: dolnośląskie, kujawsko-pomorskie, małopolskie, śląskie i pomorskie.
+– Pensje są zwykle wyższe w większych miastach, w których koszty życia są wyższe, a popyt na wykwalifikowanych specjalistów większy. W mniejszych lub gospodarczo słabiej rozwiniętych obszarach wynagrodzenia mogą być niższe. Wynika to m.in. z mniejszych kosztów utrzymania oraz mniej konkurencyjnego rynku pracy. Ważna jest także struktura firmy: duże organizacje mają większe zasoby, mogą zatem oferować lepsze warunki finansowe niż mniejsze firmy – przypomina Marta Szymańska z Manpower.</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -654,8 +853,16 @@
       <c r="D10" t="n">
         <v>0.1761384606361389</v>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Instytut Meteorologii i Gospodarki Wodnej, województwa wielkopolskiego, województwa podkarpackiego, małopolskiego, województw śląskiego, wielkopolskiego, Instytut, województwa podlaskiego, opolskiego, dolnośląskiego, województw warmińsko-mazurskiego, małopolskiego, wielkopolskiego, lubuskiego, IMGW, Instytut, Polską, Pomorzu, Wielkopolsce, Małopolsce, Podkarpaciu, Lubelszczyźnie, PAP, Marcin Chomiuk</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mazowieckie, Warszawie, województw warmińsko-mazurskiego, świętokrzyskiego, Podkarpaciu, GUS, Podlasiu, Unii Europejskiej Polska, Unii Europejskiej, dolnośląskie, kujawsko-pomorskie, śląskie, pomorskie, Marta Szymańska, Manpower</t>
+        </is>
+      </c>
       <c r="G10" t="n">
         <v>0.05882352941176471</v>
       </c>
@@ -663,12 +870,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>instytut meteorologia gospodarka wodny ostrzegł burz który miejsce być towarzyszyć silny opad deszcz grad poryw wiatr wysoki ostrzeżenie wydać południe kraj część województwo wielkopolski ostrzeżenie drugi stopień burza gradem wydać przeważający część województwo podkarpacki małopolski także część województwo śląski wielkopolski instytut prognozować burza który miejsce być towarzyszyć silny opad deszcz 40 mentymetr poryw wiatr 90 miejsce móc pojawić się grad pozostały część kraj wyjątek województwo podlaski opolski dolnośląski część województwo małopolski wielkopolski lubuski obowiązywać alerta pierwszy stopień imgw prognozywać burza który miejsce być towarzyszyć silny opad deszcz lokalnie 30 mentymetr poryw wiatr 80 miejsce grad wtorek północ instytut poinformować twitterz że polski obserwować być rozległy obszar występować burz pomorzu północny wielkopolsce małopolska podkarpaciu lubelszczyźna burza przemieszczać się kierunek alert pierwszy stopień oznaczać że móc wystąpić niebezpieczny zjawisko meteorologiczny który móc powodować strata materialny zagrożenie zdrowie życie ostrzeżenie drugi stopień oznaczać że zjawisko móc być zintensyfikować niebezpieczny pap autor Marcin chomiuk</t>
+          <t>Instytut Meteorologii i Gospodarki Wodnej ostrzegł przed burzami, którym miejscami będą towarzyszyć silne opady deszczu, grad oraz porywy wiatru. Najwyższe ostrzeżenia wydano dla południa kraju oraz dla części województwa wielkopolskiego. Ostrzeżenia drugiego stopnia przed burzami z gradem wydano dla przeważającej części województwa podkarpackiego i małopolskiego, a także dla części województw śląskiego i wielkopolskiego. Instytut prognozuje tam burze, którym miejscami będą towarzyszyć silne opady deszczu - do 40 mm, oraz porywy wiatru - do 90 km/h, miejscami może pojawić się grad.
+W pozostałej części kraju, z wyjątkiem województwa podlaskiego, opolskiego, dolnośląskiego i części województw warmińsko-mazurskiego, małopolskiego, wielkopolskiego i lubuskiego obowiązują alerty pierwszego stopnia. IMGW prognozuje tam burze, którym miejscami będą towarzyszyć silne opady deszczu - lokalnie do 30 mm oraz porywy wiatru do 80 km/h. Miejscami grad.
+We wtorek po północy Instytut poinformował na Twitterze, że nad Polską obserwowane są dwa rozległe obszary występowania burz: na Pomorzu i w północnej Wielkopolsce oraz w Małopolsce, na Podkarpaciu i Lubelszczyźnie. Burze przemieszczają się w kierunku północno-wschodnim.
+Alert pierwszego stopnia oznacza, że mogą wystąpić niebezpieczne zjawiska meteorologiczne, które mogą powodować straty materialne oraz zagrożenie dla zdrowia i życia. Ostrzeżenia drugiego stopnia oznaczają, że zjawiska te mogą być zintensyfikowane i bardziej niebezpieczne. (PAP)
+autor: Marcin Chomiuk
+mchom/ kb/</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ostrzeżenie drugi stopień burza gradem wydać przeważający część województwo podkarpacki małopolski także część województwo śląski wielkopolski instytut prognozować burza który miejsce być towarzyszyć silny opad deszcz 40 mentymetr poryw wiatr 90 miejsce móc pojawić się grad pozostały część kraj wyjątek województwo podlaski opolski dolnośląski część województwo małopolski wielkopolski lubuski obowiązywać alerta pierwszy stopień imgw prognozywać burza który miejsce być towarzyszyć silny opad deszcz lokalnie 30 mentymetr poryw wiatr 80 miejsce grad burza region wtorek północ instytut poinformować twitterz że polski obserwować być rozległy obszar występować burz pomorzu północny wielkopolsce małopolska podkarpaciu lubelszczyźna burza przemieszczać się kierunek alert pierwszy stopień oznaczać że móc wystąpić niebezpieczny zjawisko meteorologiczny który móc powodować strata materialny zagrożenie zdrowie życie ostrzeżenie drugi stopień oznaczać że zjawisko móc być zintensyfikować niebezpieczny</t>
+          <t>Ostrzeżenia drugiego stopnia przed burzami z gradem wydano dla przeważającej części województwa podkarpackiego i małopolskiego, a także dla części województw śląskiego i wielkopolskiego. Instytut prognozuje tam burze, którym miejscami będą towarzyszyć silne opady deszczu - do 40 mm, oraz porywy wiatru - do 90 km/h, miejscami może pojawić się grad.
+W pozostałej części kraju, z wyjątkiem województwa podlaskiego, opolskiego, dolnośląskiego i części województw warmińsko-mazurskiego, małopolskiego, wielkopolskiego i lubuskiego obowiązują alerty pierwszego stopnia. IMGW prognozuje tam burze, którym miejscami będą towarzyszyć silne opady deszczu - lokalnie do 30 mm oraz porywy wiatru do 80 km/h. Miejscami grad.
+Burze w wielu regionach
+We wtorek po północy Instytut poinformował na Twitterze, że nad Polską obserwowane są dwa rozległe obszary występowania burz: na Pomorzu i w północnej Wielkopolsce oraz w Małopolsce, na Podkarpaciu i Lubelszczyźnie. Burze przemieszczają się w kierunku północno-wschodnim.
+Alert pierwszego stopnia oznacza, że mogą wystąpić niebezpieczne zjawiska meteorologiczne, które mogą powodować straty materialne oraz zagrożenie dla zdrowia i życia. Ostrzeżenia drugiego stopnia oznaczają, że zjawiska te mogą być zintensyfikowane i bardziej niebezpieczne.
+pap/iar/as</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -677,8 +894,16 @@
       <c r="D11" t="n">
         <v>0.8798719048500061</v>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Instytut Meteorologii i Gospodarki Wodnej, województwa wielkopolskiego, województwa podkarpackiego, małopolskiego, województw śląskiego, wielkopolskiego, Instytut, województwa podlaskiego, opolskiego, dolnośląskiego, województw warmińsko-mazurskiego, małopolskiego, wielkopolskiego, lubuskiego, IMGW, Instytut, Polską, Pomorzu, Wielkopolsce, Małopolsce, Podkarpaciu, Lubelszczyźnie, PAP, Marcin Chomiuk</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>województwa podkarpackiego, małopolskiego, województw śląskiego, wielkopolskiego, Instytut, województwa podlaskiego, opolskiego, dolnośląskiego, województw warmińsko-mazurskiego, małopolskiego, wielkopolskiego, lubuskiego, IMGW, Instytut, Polską, Pomorzu, Wielkopolsce, Małopolsce, Podkarpaciu, Lubelszczyźnie</t>
+        </is>
+      </c>
       <c r="G11" t="n">
         <v>0.8095238095238095</v>
       </c>
